--- a/Result/profitability/3055.xlsx
+++ b/Result/profitability/3055.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.2</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.4800000000000001</v>
+        <v>-0.4112500000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>17.52125</v>
+        <v>19.785</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.54</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3587500000000001</v>
+        <v>-0.2462500000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>18.06375</v>
+        <v>19.16625</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.21</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2350000000000001</v>
+        <v>-0.1375000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>17.685</v>
+        <v>20.57625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.14375</v>
+        <v>-0.01375000000000004</v>
       </c>
       <c r="N5" t="n">
-        <v>20.135</v>
+        <v>21.01</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.4</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02124999999999996</v>
+        <v>0.05499999999999996</v>
       </c>
       <c r="N6" t="n">
-        <v>22.76</v>
+        <v>26.49</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.26</v>
       </c>
       <c r="M7" t="n">
-        <v>0.07249999999999997</v>
+        <v>0.20625</v>
       </c>
       <c r="N7" t="n">
-        <v>25.2925</v>
+        <v>27.15375</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.4</v>
       </c>
       <c r="M8" t="n">
-        <v>0.24125</v>
+        <v>0.275</v>
       </c>
       <c r="N8" t="n">
-        <v>25.63375</v>
+        <v>25.61375</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1415,7 +1415,7 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V8" t="n">
         <v>98.3</v>
@@ -1645,7 +1645,7 @@
         <v>0.5</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3599999999999999</v>
+        <v>0.36</v>
       </c>
       <c r="N10" t="n">
         <v>24.005</v>
@@ -1772,7 +1772,7 @@
         <v>1.33</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4587499999999999</v>
+        <v>0.45875</v>
       </c>
       <c r="N11" t="n">
         <v>24.47125</v>
@@ -1899,7 +1899,7 @@
         <v>0.83</v>
       </c>
       <c r="M12" t="n">
-        <v>0.5362499999999999</v>
+        <v>0.53625</v>
       </c>
       <c r="N12" t="n">
         <v>24.51375</v>
@@ -2026,7 +2026,7 @@
         <v>0.03</v>
       </c>
       <c r="M13" t="n">
-        <v>0.5312499999999999</v>
+        <v>0.53125</v>
       </c>
       <c r="N13" t="n">
         <v>23.91625</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3055</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>162</v>
+      </c>
+      <c r="D75" t="n">
+        <v>111</v>
+      </c>
+      <c r="E75" t="n">
+        <v>52</v>
+      </c>
+      <c r="F75" t="n">
+        <v>31.72</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-73</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-44.84%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>75</v>
+      </c>
+      <c r="J75" t="n">
+        <v>2</v>
+      </c>
+      <c r="K75" t="n">
+        <v>14</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.4900000000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>19.01625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.1600000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.005018820577164407</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.130434782608696</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.2831715210355987</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
